--- a/4 semester/Information Theory/ThreadEncryption/keyTable.xlsx
+++ b/4 semester/Information Theory/ThreadEncryption/keyTable.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSUIR_not_git\4 semester\Information Theory\ThreadEncryption\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSUIR\4 semester\Information Theory\ThreadEncryption\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B13121E-E4B0-4D12-9D33-C9DC3D6AF5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A70086-1D2F-42FC-A158-5079B5FF013C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,7 +67,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -89,6 +89,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -250,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -318,6 +324,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -636,7 +660,14 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" customWidth="1"/>
-    <col min="2" max="42" width="3" customWidth="1"/>
+    <col min="2" max="7" width="3" customWidth="1"/>
+    <col min="8" max="8" width="3" style="36" customWidth="1"/>
+    <col min="9" max="26" width="3" customWidth="1"/>
+    <col min="27" max="28" width="3" style="36" customWidth="1"/>
+    <col min="29" max="35" width="3" customWidth="1"/>
+    <col min="36" max="36" width="3" style="31" customWidth="1"/>
+    <col min="37" max="37" width="3" style="34" customWidth="1"/>
+    <col min="38" max="42" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:42" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -750,10 +781,10 @@
       <c r="Z2" s="19">
         <v>16</v>
       </c>
-      <c r="AA2" s="19">
+      <c r="AA2" s="8">
         <v>15</v>
       </c>
-      <c r="AB2" s="19">
+      <c r="AB2" s="8">
         <v>14</v>
       </c>
       <c r="AC2" s="19">
@@ -777,10 +808,10 @@
       <c r="AI2" s="19">
         <v>7</v>
       </c>
-      <c r="AJ2" s="8">
+      <c r="AJ2" s="29">
         <v>6</v>
       </c>
-      <c r="AK2" s="8">
+      <c r="AK2" s="32">
         <v>5</v>
       </c>
       <c r="AL2" s="19">
@@ -808,7 +839,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="21">
+      <c r="H3" s="22">
         <v>1</v>
       </c>
       <c r="I3" s="21">
@@ -865,10 +896,10 @@
       <c r="Z3" s="21">
         <v>1</v>
       </c>
-      <c r="AA3" s="21">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="21">
+      <c r="AA3" s="22">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="22">
         <v>1</v>
       </c>
       <c r="AC3" s="21">
@@ -892,10 +923,10 @@
       <c r="AI3" s="21">
         <v>1</v>
       </c>
-      <c r="AJ3" s="22">
-        <v>1</v>
-      </c>
-      <c r="AK3" s="22">
+      <c r="AJ3" s="30">
+        <v>1</v>
+      </c>
+      <c r="AK3" s="33">
         <v>1</v>
       </c>
       <c r="AL3" s="21">
@@ -924,7 +955,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="23">
+      <c r="H4" s="22">
         <f t="shared" ref="H4:W19" si="0">I3</f>
         <v>1</v>
       </c>
@@ -1000,11 +1031,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AA4" s="23">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB4" s="23">
+      <c r="AA4" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB4" s="22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -1036,11 +1067,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AJ4" s="22">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AK4" s="22">
+      <c r="AJ4" s="30">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AK4" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -1074,7 +1105,7 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="21">
+      <c r="H5" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1150,11 +1181,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AA5" s="21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB5" s="21">
+      <c r="AA5" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB5" s="22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -1186,11 +1217,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AJ5" s="22">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AK5" s="22">
+      <c r="AJ5" s="30">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AK5" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -1224,7 +1255,7 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="23">
+      <c r="H6" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1300,11 +1331,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AA6" s="23">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB6" s="23">
+      <c r="AA6" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB6" s="22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -1336,11 +1367,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AJ6" s="22">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AK6" s="22">
+      <c r="AJ6" s="30">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AK6" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -1374,7 +1405,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="21">
+      <c r="H7" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1450,11 +1481,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AA7" s="21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB7" s="21">
+      <c r="AA7" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB7" s="22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -1486,11 +1517,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AJ7" s="22">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AK7" s="22">
+      <c r="AJ7" s="30">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AK7" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -1524,7 +1555,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="21">
+      <c r="H8" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1600,11 +1631,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AA8" s="21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB8" s="21">
+      <c r="AA8" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB8" s="22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -1636,11 +1667,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AJ8" s="22">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AK8" s="22">
+      <c r="AJ8" s="30">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AK8" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1674,7 +1705,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="21">
+      <c r="H9" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1750,11 +1781,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AA9" s="21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB9" s="21">
+      <c r="AA9" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB9" s="22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -1786,11 +1817,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AJ9" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AK9" s="22">
+      <c r="AJ9" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK9" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -1824,7 +1855,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="21">
+      <c r="H10" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1900,11 +1931,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AA10" s="21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB10" s="21">
+      <c r="AA10" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB10" s="22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -1936,11 +1967,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AJ10" s="22">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AK10" s="22">
+      <c r="AJ10" s="30">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AK10" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1974,7 +2005,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="21">
+      <c r="H11" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2050,11 +2081,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AA11" s="21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB11" s="21">
+      <c r="AA11" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB11" s="22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2086,11 +2117,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AJ11" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AK11" s="22">
+      <c r="AJ11" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK11" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2124,7 +2155,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="21">
+      <c r="H12" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2200,11 +2231,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AA12" s="21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB12" s="21">
+      <c r="AA12" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB12" s="22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2236,11 +2267,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AJ12" s="22">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AK12" s="22">
+      <c r="AJ12" s="30">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AK12" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2274,7 +2305,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="21">
+      <c r="H13" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2350,11 +2381,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AA13" s="21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB13" s="21">
+      <c r="AA13" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB13" s="22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2386,11 +2417,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AJ13" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AK13" s="22">
+      <c r="AJ13" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK13" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2424,7 +2455,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="21">
+      <c r="H14" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2500,11 +2531,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AA14" s="21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB14" s="21">
+      <c r="AA14" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB14" s="22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2536,11 +2567,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AJ14" s="22">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AK14" s="22">
+      <c r="AJ14" s="30">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AK14" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2574,7 +2605,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="21">
+      <c r="H15" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2650,11 +2681,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AA15" s="21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB15" s="21">
+      <c r="AA15" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB15" s="22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2686,11 +2717,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AJ15" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AK15" s="22">
+      <c r="AJ15" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK15" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2724,7 +2755,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="21">
+      <c r="H16" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2800,11 +2831,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AA16" s="21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB16" s="21">
+      <c r="AA16" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB16" s="22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2836,11 +2867,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AJ16" s="22">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AK16" s="22">
+      <c r="AJ16" s="30">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AK16" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2874,7 +2905,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-      <c r="H17" s="21">
+      <c r="H17" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2950,11 +2981,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AA17" s="21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB17" s="21">
+      <c r="AA17" s="22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB17" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2986,11 +3017,11 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AJ17" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AK17" s="22">
+      <c r="AJ17" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK17" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3024,7 +3055,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="21">
+      <c r="H18" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -3100,11 +3131,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AA18" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB18" s="21">
+      <c r="AA18" s="22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB18" s="22">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -3136,11 +3167,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ18" s="22">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AK18" s="22">
+      <c r="AJ18" s="30">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AK18" s="33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3174,7 +3205,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-      <c r="H19" s="21">
+      <c r="H19" s="22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -3250,11 +3281,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA19" s="21">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AB19" s="21">
+      <c r="AA19" s="22">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AB19" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3286,11 +3317,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AJ19" s="22">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AK19" s="22">
+      <c r="AJ19" s="30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AK19" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -3324,7 +3355,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-      <c r="H20" s="21">
+      <c r="H20" s="22">
         <f t="shared" ref="H20:W35" si="6">I19</f>
         <v>1</v>
       </c>
@@ -3400,11 +3431,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AA20" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB20" s="21">
+      <c r="AA20" s="22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB20" s="22">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -3436,11 +3467,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ20" s="22">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AK20" s="22">
+      <c r="AJ20" s="30">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AK20" s="33">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3474,7 +3505,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="21">
+      <c r="H21" s="22">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -3550,11 +3581,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA21" s="21">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AB21" s="21">
+      <c r="AA21" s="22">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AB21" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3586,11 +3617,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AJ21" s="22">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AK21" s="22">
+      <c r="AJ21" s="30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AK21" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -3624,7 +3655,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="21">
+      <c r="H22" s="22">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -3700,11 +3731,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AA22" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB22" s="21">
+      <c r="AA22" s="22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB22" s="22">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -3736,11 +3767,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ22" s="22">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AK22" s="22">
+      <c r="AJ22" s="30">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AK22" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -3774,7 +3805,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="21">
+      <c r="H23" s="22">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -3850,11 +3881,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA23" s="21">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AB23" s="21">
+      <c r="AA23" s="22">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AB23" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3886,11 +3917,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AJ23" s="22">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AK23" s="22">
+      <c r="AJ23" s="30">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AK23" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -3924,7 +3955,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="21">
+      <c r="H24" s="22">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -4000,11 +4031,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AA24" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB24" s="21">
+      <c r="AA24" s="22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB24" s="22">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -4036,11 +4067,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AJ24" s="22">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AK24" s="22">
+      <c r="AJ24" s="30">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AK24" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -4074,7 +4105,7 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="21">
+      <c r="H25" s="22">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -4150,11 +4181,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA25" s="21">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AB25" s="21">
+      <c r="AA25" s="22">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AB25" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4186,11 +4217,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AJ25" s="22">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AK25" s="22">
+      <c r="AJ25" s="30">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AK25" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -4224,7 +4255,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-      <c r="H26" s="21">
+      <c r="H26" s="22">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -4300,11 +4331,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AA26" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB26" s="21">
+      <c r="AA26" s="22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB26" s="22">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -4336,11 +4367,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AJ26" s="22">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AK26" s="22">
+      <c r="AJ26" s="30">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AK26" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -4374,7 +4405,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="21">
+      <c r="H27" s="22">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -4450,11 +4481,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA27" s="21">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AB27" s="21">
+      <c r="AA27" s="22">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AB27" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4486,11 +4517,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AJ27" s="22">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AK27" s="22">
+      <c r="AJ27" s="30">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AK27" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -4524,7 +4555,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-      <c r="H28" s="21">
+      <c r="H28" s="22">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -4600,11 +4631,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AA28" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB28" s="21">
+      <c r="AA28" s="22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB28" s="22">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -4636,11 +4667,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AJ28" s="22">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AK28" s="22">
+      <c r="AJ28" s="30">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AK28" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -4674,7 +4705,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="21">
+      <c r="H29" s="22">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -4750,11 +4781,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA29" s="21">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AB29" s="21">
+      <c r="AA29" s="22">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AB29" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4786,11 +4817,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AJ29" s="22">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AK29" s="22">
+      <c r="AJ29" s="30">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AK29" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -4824,7 +4855,7 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="21">
+      <c r="H30" s="22">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -4900,11 +4931,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AA30" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB30" s="21">
+      <c r="AA30" s="22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB30" s="22">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -4936,11 +4967,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AJ30" s="22">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AK30" s="22">
+      <c r="AJ30" s="30">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AK30" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -4974,7 +5005,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="21">
+      <c r="H31" s="22">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -5050,11 +5081,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA31" s="21">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AB31" s="21">
+      <c r="AA31" s="22">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AB31" s="22">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -5086,11 +5117,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AJ31" s="22">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AK31" s="22">
+      <c r="AJ31" s="30">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AK31" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -5124,7 +5155,7 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="21">
+      <c r="H32" s="22">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -5200,11 +5231,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AA32" s="21">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AB32" s="21">
+      <c r="AA32" s="22">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AB32" s="22">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -5236,11 +5267,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AJ32" s="22">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AK32" s="22">
+      <c r="AJ32" s="30">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AK32" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -5274,7 +5305,7 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-      <c r="H33" s="21">
+      <c r="H33" s="22">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -5350,11 +5381,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AA33" s="21">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AB33" s="21">
+      <c r="AA33" s="22">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AB33" s="22">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -5386,11 +5417,11 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AJ33" s="22">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AK33" s="22">
+      <c r="AJ33" s="30">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AK33" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -5424,7 +5455,7 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
-      <c r="H34" s="21">
+      <c r="H34" s="22">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -5500,11 +5531,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AA34" s="21">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AB34" s="21">
+      <c r="AA34" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AB34" s="22">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -5536,11 +5567,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AJ34" s="22">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AK34" s="22">
+      <c r="AJ34" s="30">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AK34" s="33">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -5574,7 +5605,7 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="H35" s="21">
+      <c r="H35" s="22">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -5650,11 +5681,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AA35" s="21">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AB35" s="21">
+      <c r="AA35" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AB35" s="22">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -5686,11 +5717,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AJ35" s="22">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AK35" s="22">
+      <c r="AJ35" s="30">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AK35" s="33">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -5724,7 +5755,7 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
-      <c r="H36" s="21">
+      <c r="H36" s="22">
         <f t="shared" ref="H36:V52" si="10">I35</f>
         <v>1</v>
       </c>
@@ -5800,11 +5831,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AA36" s="21">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AB36" s="21">
+      <c r="AA36" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AB36" s="22">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -5836,11 +5867,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AJ36" s="22">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AK36" s="22">
+      <c r="AJ36" s="30">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AK36" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -5874,7 +5905,7 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="21">
+      <c r="H37" s="22">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -5950,11 +5981,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AA37" s="21">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AB37" s="21">
+      <c r="AA37" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AB37" s="22">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -5986,11 +6017,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AJ37" s="22">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AK37" s="22">
+      <c r="AJ37" s="30">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AK37" s="33">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -6024,7 +6055,7 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-      <c r="H38" s="21">
+      <c r="H38" s="22">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -6100,11 +6131,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AA38" s="21">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AB38" s="21">
+      <c r="AA38" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AB38" s="22">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -6136,11 +6167,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ38" s="22">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AK38" s="22">
+      <c r="AJ38" s="30">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AK38" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -6174,7 +6205,7 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-      <c r="H39" s="21">
+      <c r="H39" s="22">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -6250,11 +6281,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AA39" s="21">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AB39" s="21">
+      <c r="AA39" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AB39" s="22">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -6286,11 +6317,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AJ39" s="22">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AK39" s="22">
+      <c r="AJ39" s="30">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AK39" s="33">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -6324,7 +6355,7 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="21">
+      <c r="H40" s="22">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -6400,11 +6431,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AA40" s="21">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AB40" s="21">
+      <c r="AA40" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AB40" s="22">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -6436,11 +6467,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ40" s="22">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AK40" s="22">
+      <c r="AJ40" s="30">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AK40" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -6474,7 +6505,7 @@
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-      <c r="H41" s="21">
+      <c r="H41" s="22">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -6550,11 +6581,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AA41" s="21">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AB41" s="21">
+      <c r="AA41" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AB41" s="22">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -6586,11 +6617,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AJ41" s="22">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AK41" s="22">
+      <c r="AJ41" s="30">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AK41" s="33">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -6624,7 +6655,7 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="21">
+      <c r="H42" s="22">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -6700,11 +6731,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AA42" s="21">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AB42" s="21">
+      <c r="AA42" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AB42" s="22">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -6736,11 +6767,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ42" s="22">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AK42" s="22">
+      <c r="AJ42" s="30">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AK42" s="33">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -6774,7 +6805,7 @@
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
-      <c r="H43" s="21">
+      <c r="H43" s="22">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -6850,11 +6881,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AA43" s="21">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AB43" s="21">
+      <c r="AA43" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AB43" s="22">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -6886,11 +6917,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AJ43" s="22">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AK43" s="22">
+      <c r="AJ43" s="30">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AK43" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -6924,7 +6955,7 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="21">
+      <c r="H44" s="22">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -7000,11 +7031,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AA44" s="21">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AB44" s="21">
+      <c r="AA44" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AB44" s="22">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -7036,11 +7067,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AJ44" s="22">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AK44" s="22">
+      <c r="AJ44" s="30">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AK44" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -7074,7 +7105,7 @@
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
-      <c r="H45" s="21">
+      <c r="H45" s="22">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -7150,11 +7181,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AA45" s="21">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AB45" s="21">
+      <c r="AA45" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AB45" s="22">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -7186,11 +7217,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ45" s="22">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AK45" s="22">
+      <c r="AJ45" s="30">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AK45" s="33">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -7224,7 +7255,7 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="21">
+      <c r="H46" s="22">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -7300,11 +7331,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AA46" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AB46" s="21">
+      <c r="AA46" s="22">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AB46" s="22">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -7336,11 +7367,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ46" s="22">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AK46" s="22">
+      <c r="AJ46" s="30">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AK46" s="33">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -7374,7 +7405,7 @@
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
-      <c r="H47" s="21">
+      <c r="H47" s="22">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -7450,11 +7481,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA47" s="21">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AB47" s="21">
+      <c r="AA47" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AB47" s="22">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -7486,11 +7517,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AJ47" s="22">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AK47" s="22">
+      <c r="AJ47" s="30">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AK47" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -7524,7 +7555,7 @@
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="21">
+      <c r="H48" s="22">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -7600,11 +7631,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AA48" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AB48" s="21">
+      <c r="AA48" s="22">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AB48" s="22">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -7636,11 +7667,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AJ48" s="22">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AK48" s="22">
+      <c r="AJ48" s="30">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AK48" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -7674,7 +7705,7 @@
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="21">
+      <c r="H49" s="22">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -7750,11 +7781,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA49" s="21">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AB49" s="21">
+      <c r="AA49" s="22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AB49" s="22">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -7786,11 +7817,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ49" s="22">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AK49" s="22">
+      <c r="AJ49" s="30">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AK49" s="33">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -7824,7 +7855,7 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="21">
+      <c r="H50" s="22">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -7900,11 +7931,11 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AA50" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AB50" s="21">
+      <c r="AA50" s="22">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AB50" s="22">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -7936,11 +7967,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ50" s="22">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AK50" s="22">
+      <c r="AJ50" s="30">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AK50" s="33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -7974,7 +8005,7 @@
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="21">
+      <c r="H51" s="22">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -8050,11 +8081,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AA51" s="21">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AB51" s="21">
+      <c r="AA51" s="22">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AB51" s="22">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -8086,11 +8117,11 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AJ51" s="22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AK51" s="22">
+      <c r="AJ51" s="30">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK51" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8124,7 +8155,7 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="21">
+      <c r="H52" s="22">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -8200,11 +8231,11 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AA52" s="21">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AB52" s="21">
+      <c r="AA52" s="22">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AB52" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8236,11 +8267,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AJ52" s="22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AK52" s="22">
+      <c r="AJ52" s="30">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK52" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -8274,7 +8305,7 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
-      <c r="H53" s="21">
+      <c r="H53" s="22">
         <f t="shared" ref="H53:W69" si="11">I52</f>
         <v>1</v>
       </c>
@@ -8350,11 +8381,11 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AA53" s="21">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB53" s="21">
+      <c r="AA53" s="22">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB53" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8386,11 +8417,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AJ53" s="22">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AK53" s="22">
+      <c r="AJ53" s="30">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AK53" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -8424,7 +8455,7 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="21">
+      <c r="H54" s="22">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -8500,11 +8531,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AA54" s="21">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB54" s="21">
+      <c r="AA54" s="22">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB54" s="22">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -8536,11 +8567,11 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AJ54" s="22">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AK54" s="22">
+      <c r="AJ54" s="30">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AK54" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8574,7 +8605,7 @@
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
-      <c r="H55" s="21">
+      <c r="H55" s="22">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -8650,11 +8681,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AA55" s="21">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AB55" s="21">
+      <c r="AA55" s="22">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AB55" s="22">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -8686,11 +8717,11 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AJ55" s="22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AK55" s="22">
+      <c r="AJ55" s="30">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK55" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8724,7 +8755,7 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="21">
+      <c r="H56" s="22">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -8800,11 +8831,11 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AA56" s="21">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AB56" s="21">
+      <c r="AA56" s="22">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AB56" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8836,11 +8867,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AJ56" s="22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AK56" s="22">
+      <c r="AJ56" s="30">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK56" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -8874,7 +8905,7 @@
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
-      <c r="H57" s="21">
+      <c r="H57" s="22">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -8950,11 +8981,11 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AA57" s="21">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB57" s="21">
+      <c r="AA57" s="22">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB57" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8986,11 +9017,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AJ57" s="22">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AK57" s="22">
+      <c r="AJ57" s="30">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AK57" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -9024,7 +9055,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
-      <c r="H58" s="21">
+      <c r="H58" s="22">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -9100,11 +9131,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AA58" s="21">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB58" s="21">
+      <c r="AA58" s="22">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB58" s="22">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -9136,11 +9167,11 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AJ58" s="22">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AK58" s="22">
+      <c r="AJ58" s="30">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AK58" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9173,7 +9204,7 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
-      <c r="H59" s="21">
+      <c r="H59" s="22">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -9249,11 +9280,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AA59" s="21">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AB59" s="21">
+      <c r="AA59" s="22">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AB59" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9285,11 +9316,11 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AJ59" s="22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AK59" s="22">
+      <c r="AJ59" s="30">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK59" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9322,7 +9353,7 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="21">
+      <c r="H60" s="22">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -9398,11 +9429,11 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AA60" s="21">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB60" s="21">
+      <c r="AA60" s="22">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB60" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9434,11 +9465,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AJ60" s="22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AK60" s="22">
+      <c r="AJ60" s="30">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK60" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -9471,7 +9502,7 @@
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="21">
+      <c r="H61" s="22">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -9547,11 +9578,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AA61" s="21">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB61" s="21">
+      <c r="AA61" s="22">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB61" s="22">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -9583,11 +9614,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AJ61" s="22">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AK61" s="22">
+      <c r="AJ61" s="30">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AK61" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -9620,7 +9651,7 @@
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="21">
+      <c r="H62" s="22">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -9696,11 +9727,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AA62" s="21">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AB62" s="21">
+      <c r="AA62" s="22">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AB62" s="22">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -9732,11 +9763,11 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AJ62" s="22">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AK62" s="22">
+      <c r="AJ62" s="30">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AK62" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9769,7 +9800,7 @@
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
-      <c r="H63" s="21">
+      <c r="H63" s="22">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -9845,11 +9876,11 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AA63" s="21">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AB63" s="21">
+      <c r="AA63" s="22">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AB63" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9881,11 +9912,11 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AJ63" s="22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AK63" s="22">
+      <c r="AJ63" s="30">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK63" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9918,7 +9949,7 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="21">
+      <c r="H64" s="22">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -9994,11 +10025,11 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AA64" s="21">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AB64" s="21">
+      <c r="AA64" s="22">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB64" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10030,11 +10061,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AJ64" s="22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AK64" s="22">
+      <c r="AJ64" s="30">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK64" s="33">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10067,7 +10098,7 @@
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
-      <c r="H65" s="21">
+      <c r="H65" s="22">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -10143,11 +10174,11 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA65" s="21">
+      <c r="AA65" s="22">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AB65" s="21">
+      <c r="AB65" s="22">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
@@ -10179,11 +10210,11 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AJ65" s="22">
+      <c r="AJ65" s="30">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AK65" s="22">
+      <c r="AK65" s="33">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
@@ -10216,7 +10247,7 @@
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="21">
+      <c r="H66" s="22">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -10292,11 +10323,11 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA66" s="21">
+      <c r="AA66" s="22">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AB66" s="21">
+      <c r="AB66" s="22">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
@@ -10328,11 +10359,11 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AJ66" s="22">
+      <c r="AJ66" s="30">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AK66" s="22">
+      <c r="AK66" s="33">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
@@ -10365,7 +10396,7 @@
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
-      <c r="H67" s="21">
+      <c r="H67" s="22">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -10441,11 +10472,11 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AA67" s="21">
+      <c r="AA67" s="22">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AB67" s="21">
+      <c r="AB67" s="22">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -10477,11 +10508,11 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AJ67" s="22">
+      <c r="AJ67" s="30">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AK67" s="22">
+      <c r="AK67" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -10514,7 +10545,7 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="21">
+      <c r="H68" s="22">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -10590,11 +10621,11 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AA68" s="21">
+      <c r="AA68" s="22">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AB68" s="21">
+      <c r="AB68" s="22">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -10626,11 +10657,11 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AJ68" s="22">
+      <c r="AJ68" s="30">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AK68" s="22">
+      <c r="AK68" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -10663,7 +10694,7 @@
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
-      <c r="H69" s="21">
+      <c r="H69" s="22">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -10739,11 +10770,11 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA69" s="21">
+      <c r="AA69" s="22">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AB69" s="21">
+      <c r="AB69" s="22">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
@@ -10775,11 +10806,11 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AJ69" s="22">
+      <c r="AJ69" s="30">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AK69" s="22">
+      <c r="AK69" s="33">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
@@ -10812,7 +10843,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
-      <c r="H70" s="21">
+      <c r="H70" s="22">
         <f t="shared" ref="H70:R70" si="15">I69</f>
         <v>1</v>
       </c>
@@ -10888,11 +10919,11 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA70" s="21">
+      <c r="AA70" s="22">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AB70" s="21">
+      <c r="AB70" s="22">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
@@ -10924,11 +10955,11 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AJ70" s="22">
+      <c r="AJ70" s="30">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AK70" s="22">
+      <c r="AK70" s="33">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -10961,7 +10992,7 @@
       <c r="E95" s="16"/>
       <c r="F95" s="16"/>
       <c r="G95" s="16"/>
-      <c r="H95" s="16"/>
+      <c r="H95" s="35"/>
       <c r="I95" s="16"/>
       <c r="J95" s="16"/>
       <c r="K95" s="16"/>
@@ -10980,8 +11011,8 @@
       <c r="X95" s="16"/>
       <c r="Y95" s="16"/>
       <c r="Z95" s="16"/>
-      <c r="AA95" s="16"/>
-      <c r="AB95" s="16"/>
+      <c r="AA95" s="35"/>
+      <c r="AB95" s="35"/>
       <c r="AC95" s="16"/>
       <c r="AD95" s="16"/>
       <c r="AE95" s="16"/>
@@ -10994,7 +11025,7 @@
       <c r="E96" s="16"/>
       <c r="F96" s="16"/>
       <c r="G96" s="16"/>
-      <c r="H96" s="16"/>
+      <c r="H96" s="35"/>
       <c r="I96" s="16"/>
       <c r="J96" s="16"/>
       <c r="K96" s="16"/>
@@ -11013,8 +11044,8 @@
       <c r="X96" s="16"/>
       <c r="Y96" s="16"/>
       <c r="Z96" s="16"/>
-      <c r="AA96" s="16"/>
-      <c r="AB96" s="16"/>
+      <c r="AA96" s="35"/>
+      <c r="AB96" s="35"/>
       <c r="AC96" s="16"/>
       <c r="AD96" s="16"/>
       <c r="AE96" s="16"/>
@@ -11027,7 +11058,7 @@
       <c r="E97" s="16"/>
       <c r="F97" s="16"/>
       <c r="G97" s="16"/>
-      <c r="H97" s="16"/>
+      <c r="H97" s="35"/>
       <c r="I97" s="16"/>
       <c r="J97" s="16"/>
       <c r="K97" s="16"/>
@@ -11046,8 +11077,8 @@
       <c r="X97" s="16"/>
       <c r="Y97" s="16"/>
       <c r="Z97" s="16"/>
-      <c r="AA97" s="16"/>
-      <c r="AB97" s="16"/>
+      <c r="AA97" s="35"/>
+      <c r="AB97" s="35"/>
       <c r="AC97" s="16"/>
       <c r="AD97" s="16"/>
       <c r="AE97" s="16"/>
@@ -11060,7 +11091,7 @@
       <c r="E98" s="16"/>
       <c r="F98" s="16"/>
       <c r="G98" s="16"/>
-      <c r="H98" s="16"/>
+      <c r="H98" s="35"/>
       <c r="I98" s="16"/>
       <c r="J98" s="16"/>
       <c r="K98" s="16"/>
@@ -11079,8 +11110,8 @@
       <c r="X98" s="16"/>
       <c r="Y98" s="16"/>
       <c r="Z98" s="16"/>
-      <c r="AA98" s="16"/>
-      <c r="AB98" s="16"/>
+      <c r="AA98" s="35"/>
+      <c r="AB98" s="35"/>
       <c r="AC98" s="16"/>
       <c r="AD98" s="16"/>
       <c r="AE98" s="16"/>
@@ -11093,7 +11124,7 @@
       <c r="E99" s="16"/>
       <c r="F99" s="16"/>
       <c r="G99" s="16"/>
-      <c r="H99" s="16"/>
+      <c r="H99" s="35"/>
       <c r="I99" s="16"/>
       <c r="J99" s="16"/>
       <c r="K99" s="16"/>
@@ -11112,8 +11143,8 @@
       <c r="X99" s="16"/>
       <c r="Y99" s="16"/>
       <c r="Z99" s="16"/>
-      <c r="AA99" s="16"/>
-      <c r="AB99" s="16"/>
+      <c r="AA99" s="35"/>
+      <c r="AB99" s="35"/>
       <c r="AC99" s="16"/>
       <c r="AD99" s="16"/>
       <c r="AE99" s="16"/>
@@ -11126,7 +11157,7 @@
       <c r="E100" s="16"/>
       <c r="F100" s="16"/>
       <c r="G100" s="16"/>
-      <c r="H100" s="16"/>
+      <c r="H100" s="35"/>
       <c r="I100" s="16"/>
       <c r="J100" s="16"/>
       <c r="K100" s="16"/>
@@ -11145,8 +11176,8 @@
       <c r="X100" s="16"/>
       <c r="Y100" s="16"/>
       <c r="Z100" s="16"/>
-      <c r="AA100" s="16"/>
-      <c r="AB100" s="16"/>
+      <c r="AA100" s="35"/>
+      <c r="AB100" s="35"/>
       <c r="AC100" s="16"/>
       <c r="AD100" s="16"/>
       <c r="AE100" s="16"/>
@@ -11159,7 +11190,7 @@
       <c r="E101" s="16"/>
       <c r="F101" s="16"/>
       <c r="G101" s="16"/>
-      <c r="H101" s="16"/>
+      <c r="H101" s="35"/>
       <c r="I101" s="16"/>
       <c r="J101" s="16"/>
       <c r="K101" s="16"/>
@@ -11178,8 +11209,8 @@
       <c r="X101" s="16"/>
       <c r="Y101" s="16"/>
       <c r="Z101" s="16"/>
-      <c r="AA101" s="16"/>
-      <c r="AB101" s="16"/>
+      <c r="AA101" s="35"/>
+      <c r="AB101" s="35"/>
       <c r="AC101" s="16"/>
       <c r="AD101" s="16"/>
       <c r="AE101" s="16"/>
@@ -11192,7 +11223,7 @@
       <c r="E102" s="16"/>
       <c r="F102" s="16"/>
       <c r="G102" s="16"/>
-      <c r="H102" s="16"/>
+      <c r="H102" s="35"/>
       <c r="I102" s="16"/>
       <c r="J102" s="16"/>
       <c r="K102" s="16"/>
@@ -11211,8 +11242,8 @@
       <c r="X102" s="16"/>
       <c r="Y102" s="16"/>
       <c r="Z102" s="16"/>
-      <c r="AA102" s="16"/>
-      <c r="AB102" s="16"/>
+      <c r="AA102" s="35"/>
+      <c r="AB102" s="35"/>
       <c r="AC102" s="16"/>
       <c r="AD102" s="16"/>
       <c r="AE102" s="16"/>
@@ -11225,7 +11256,7 @@
       <c r="E103" s="16"/>
       <c r="F103" s="16"/>
       <c r="G103" s="16"/>
-      <c r="H103" s="16"/>
+      <c r="H103" s="35"/>
       <c r="I103" s="16"/>
       <c r="J103" s="16"/>
       <c r="K103" s="16"/>
@@ -11244,8 +11275,8 @@
       <c r="X103" s="16"/>
       <c r="Y103" s="16"/>
       <c r="Z103" s="16"/>
-      <c r="AA103" s="16"/>
-      <c r="AB103" s="16"/>
+      <c r="AA103" s="35"/>
+      <c r="AB103" s="35"/>
       <c r="AC103" s="16"/>
       <c r="AD103" s="16"/>
       <c r="AE103" s="16"/>
@@ -11258,7 +11289,7 @@
       <c r="E104" s="16"/>
       <c r="F104" s="16"/>
       <c r="G104" s="16"/>
-      <c r="H104" s="16"/>
+      <c r="H104" s="35"/>
       <c r="I104" s="16"/>
       <c r="J104" s="16"/>
       <c r="K104" s="16"/>
@@ -11277,8 +11308,8 @@
       <c r="X104" s="16"/>
       <c r="Y104" s="16"/>
       <c r="Z104" s="16"/>
-      <c r="AA104" s="16"/>
-      <c r="AB104" s="16"/>
+      <c r="AA104" s="35"/>
+      <c r="AB104" s="35"/>
       <c r="AC104" s="16"/>
       <c r="AD104" s="16"/>
       <c r="AE104" s="16"/>
@@ -11291,7 +11322,7 @@
       <c r="E105" s="16"/>
       <c r="F105" s="16"/>
       <c r="G105" s="16"/>
-      <c r="H105" s="16"/>
+      <c r="H105" s="35"/>
       <c r="I105" s="16"/>
       <c r="J105" s="16"/>
       <c r="K105" s="16"/>
@@ -11310,8 +11341,8 @@
       <c r="X105" s="16"/>
       <c r="Y105" s="16"/>
       <c r="Z105" s="16"/>
-      <c r="AA105" s="16"/>
-      <c r="AB105" s="16"/>
+      <c r="AA105" s="35"/>
+      <c r="AB105" s="35"/>
       <c r="AC105" s="16"/>
       <c r="AD105" s="16"/>
       <c r="AE105" s="16"/>
@@ -11324,7 +11355,7 @@
       <c r="E106" s="16"/>
       <c r="F106" s="16"/>
       <c r="G106" s="16"/>
-      <c r="H106" s="16"/>
+      <c r="H106" s="35"/>
       <c r="I106" s="16"/>
       <c r="J106" s="16"/>
       <c r="K106" s="16"/>
@@ -11343,8 +11374,8 @@
       <c r="X106" s="16"/>
       <c r="Y106" s="16"/>
       <c r="Z106" s="16"/>
-      <c r="AA106" s="16"/>
-      <c r="AB106" s="16"/>
+      <c r="AA106" s="35"/>
+      <c r="AB106" s="35"/>
       <c r="AC106" s="16"/>
       <c r="AD106" s="16"/>
       <c r="AE106" s="16"/>
@@ -11357,7 +11388,7 @@
       <c r="E107" s="16"/>
       <c r="F107" s="16"/>
       <c r="G107" s="16"/>
-      <c r="H107" s="16"/>
+      <c r="H107" s="35"/>
       <c r="I107" s="16"/>
       <c r="J107" s="16"/>
       <c r="K107" s="16"/>
@@ -11376,8 +11407,8 @@
       <c r="X107" s="16"/>
       <c r="Y107" s="16"/>
       <c r="Z107" s="16"/>
-      <c r="AA107" s="16"/>
-      <c r="AB107" s="16"/>
+      <c r="AA107" s="35"/>
+      <c r="AB107" s="35"/>
       <c r="AC107" s="16"/>
       <c r="AD107" s="16"/>
       <c r="AE107" s="16"/>
@@ -11390,7 +11421,7 @@
       <c r="E108" s="16"/>
       <c r="F108" s="16"/>
       <c r="G108" s="16"/>
-      <c r="H108" s="16"/>
+      <c r="H108" s="35"/>
       <c r="I108" s="16"/>
       <c r="J108" s="16"/>
       <c r="K108" s="16"/>
@@ -11409,8 +11440,8 @@
       <c r="X108" s="16"/>
       <c r="Y108" s="16"/>
       <c r="Z108" s="16"/>
-      <c r="AA108" s="16"/>
-      <c r="AB108" s="16"/>
+      <c r="AA108" s="35"/>
+      <c r="AB108" s="35"/>
       <c r="AC108" s="16"/>
       <c r="AD108" s="16"/>
       <c r="AE108" s="16"/>
@@ -11423,7 +11454,7 @@
       <c r="E109" s="16"/>
       <c r="F109" s="16"/>
       <c r="G109" s="16"/>
-      <c r="H109" s="16"/>
+      <c r="H109" s="35"/>
       <c r="I109" s="16"/>
       <c r="J109" s="16"/>
       <c r="K109" s="16"/>
@@ -11442,8 +11473,8 @@
       <c r="X109" s="16"/>
       <c r="Y109" s="16"/>
       <c r="Z109" s="16"/>
-      <c r="AA109" s="16"/>
-      <c r="AB109" s="16"/>
+      <c r="AA109" s="35"/>
+      <c r="AB109" s="35"/>
       <c r="AC109" s="16"/>
       <c r="AD109" s="16"/>
       <c r="AE109" s="16"/>
@@ -11456,7 +11487,7 @@
       <c r="E110" s="16"/>
       <c r="F110" s="16"/>
       <c r="G110" s="16"/>
-      <c r="H110" s="16"/>
+      <c r="H110" s="35"/>
       <c r="I110" s="16"/>
       <c r="J110" s="16"/>
       <c r="K110" s="16"/>
@@ -11475,8 +11506,8 @@
       <c r="X110" s="16"/>
       <c r="Y110" s="16"/>
       <c r="Z110" s="16"/>
-      <c r="AA110" s="16"/>
-      <c r="AB110" s="16"/>
+      <c r="AA110" s="35"/>
+      <c r="AB110" s="35"/>
       <c r="AC110" s="16"/>
       <c r="AD110" s="16"/>
       <c r="AE110" s="16"/>
@@ -11489,7 +11520,7 @@
       <c r="E111" s="16"/>
       <c r="F111" s="16"/>
       <c r="G111" s="16"/>
-      <c r="H111" s="16"/>
+      <c r="H111" s="35"/>
       <c r="I111" s="16"/>
       <c r="J111" s="16"/>
       <c r="K111" s="16"/>
@@ -11508,8 +11539,8 @@
       <c r="X111" s="16"/>
       <c r="Y111" s="16"/>
       <c r="Z111" s="16"/>
-      <c r="AA111" s="16"/>
-      <c r="AB111" s="16"/>
+      <c r="AA111" s="35"/>
+      <c r="AB111" s="35"/>
       <c r="AC111" s="16"/>
       <c r="AD111" s="16"/>
       <c r="AE111" s="16"/>
@@ -11522,7 +11553,7 @@
       <c r="E112" s="16"/>
       <c r="F112" s="16"/>
       <c r="G112" s="16"/>
-      <c r="H112" s="16"/>
+      <c r="H112" s="35"/>
       <c r="I112" s="16"/>
       <c r="J112" s="16"/>
       <c r="K112" s="16"/>
@@ -11541,8 +11572,8 @@
       <c r="X112" s="16"/>
       <c r="Y112" s="16"/>
       <c r="Z112" s="16"/>
-      <c r="AA112" s="16"/>
-      <c r="AB112" s="16"/>
+      <c r="AA112" s="35"/>
+      <c r="AB112" s="35"/>
       <c r="AC112" s="16"/>
       <c r="AD112" s="16"/>
       <c r="AE112" s="16"/>
@@ -11555,7 +11586,7 @@
       <c r="E113" s="16"/>
       <c r="F113" s="16"/>
       <c r="G113" s="16"/>
-      <c r="H113" s="16"/>
+      <c r="H113" s="35"/>
       <c r="I113" s="16"/>
       <c r="J113" s="16"/>
       <c r="K113" s="16"/>
@@ -11574,8 +11605,8 @@
       <c r="X113" s="16"/>
       <c r="Y113" s="16"/>
       <c r="Z113" s="16"/>
-      <c r="AA113" s="16"/>
-      <c r="AB113" s="16"/>
+      <c r="AA113" s="35"/>
+      <c r="AB113" s="35"/>
       <c r="AC113" s="16"/>
       <c r="AD113" s="16"/>
       <c r="AE113" s="16"/>
@@ -11588,7 +11619,7 @@
       <c r="E114" s="16"/>
       <c r="F114" s="16"/>
       <c r="G114" s="16"/>
-      <c r="H114" s="16"/>
+      <c r="H114" s="35"/>
       <c r="I114" s="16"/>
       <c r="J114" s="16"/>
       <c r="K114" s="16"/>
@@ -11607,8 +11638,8 @@
       <c r="X114" s="16"/>
       <c r="Y114" s="16"/>
       <c r="Z114" s="16"/>
-      <c r="AA114" s="16"/>
-      <c r="AB114" s="16"/>
+      <c r="AA114" s="35"/>
+      <c r="AB114" s="35"/>
       <c r="AC114" s="16"/>
       <c r="AD114" s="16"/>
       <c r="AE114" s="16"/>
@@ -11621,7 +11652,7 @@
       <c r="E115" s="16"/>
       <c r="F115" s="16"/>
       <c r="G115" s="16"/>
-      <c r="H115" s="16"/>
+      <c r="H115" s="35"/>
       <c r="I115" s="16"/>
       <c r="J115" s="16"/>
       <c r="K115" s="16"/>
@@ -11640,8 +11671,8 @@
       <c r="X115" s="16"/>
       <c r="Y115" s="16"/>
       <c r="Z115" s="16"/>
-      <c r="AA115" s="16"/>
-      <c r="AB115" s="16"/>
+      <c r="AA115" s="35"/>
+      <c r="AB115" s="35"/>
       <c r="AC115" s="16"/>
       <c r="AD115" s="16"/>
       <c r="AE115" s="16"/>
@@ -11654,7 +11685,7 @@
       <c r="E116" s="16"/>
       <c r="F116" s="16"/>
       <c r="G116" s="16"/>
-      <c r="H116" s="16"/>
+      <c r="H116" s="35"/>
       <c r="I116" s="16"/>
       <c r="J116" s="16"/>
       <c r="K116" s="16"/>
@@ -11673,8 +11704,8 @@
       <c r="X116" s="16"/>
       <c r="Y116" s="16"/>
       <c r="Z116" s="16"/>
-      <c r="AA116" s="16"/>
-      <c r="AB116" s="16"/>
+      <c r="AA116" s="35"/>
+      <c r="AB116" s="35"/>
       <c r="AC116" s="16"/>
       <c r="AD116" s="16"/>
       <c r="AE116" s="16"/>
@@ -11687,7 +11718,7 @@
       <c r="E117" s="16"/>
       <c r="F117" s="16"/>
       <c r="G117" s="16"/>
-      <c r="H117" s="16"/>
+      <c r="H117" s="35"/>
       <c r="I117" s="16"/>
       <c r="J117" s="16"/>
       <c r="K117" s="16"/>
@@ -11706,8 +11737,8 @@
       <c r="X117" s="16"/>
       <c r="Y117" s="16"/>
       <c r="Z117" s="16"/>
-      <c r="AA117" s="16"/>
-      <c r="AB117" s="16"/>
+      <c r="AA117" s="35"/>
+      <c r="AB117" s="35"/>
       <c r="AC117" s="16"/>
       <c r="AD117" s="16"/>
       <c r="AE117" s="16"/>
@@ -11720,7 +11751,7 @@
       <c r="E118" s="16"/>
       <c r="F118" s="16"/>
       <c r="G118" s="16"/>
-      <c r="H118" s="16"/>
+      <c r="H118" s="35"/>
       <c r="I118" s="16"/>
       <c r="J118" s="16"/>
       <c r="K118" s="16"/>
@@ -11739,8 +11770,8 @@
       <c r="X118" s="16"/>
       <c r="Y118" s="16"/>
       <c r="Z118" s="16"/>
-      <c r="AA118" s="16"/>
-      <c r="AB118" s="16"/>
+      <c r="AA118" s="35"/>
+      <c r="AB118" s="35"/>
       <c r="AC118" s="16"/>
       <c r="AD118" s="16"/>
       <c r="AE118" s="16"/>
@@ -11753,7 +11784,7 @@
       <c r="E119" s="16"/>
       <c r="F119" s="16"/>
       <c r="G119" s="16"/>
-      <c r="H119" s="16"/>
+      <c r="H119" s="35"/>
       <c r="I119" s="16"/>
       <c r="J119" s="16"/>
       <c r="K119" s="16"/>
@@ -11772,8 +11803,8 @@
       <c r="X119" s="16"/>
       <c r="Y119" s="16"/>
       <c r="Z119" s="16"/>
-      <c r="AA119" s="16"/>
-      <c r="AB119" s="16"/>
+      <c r="AA119" s="35"/>
+      <c r="AB119" s="35"/>
       <c r="AC119" s="16"/>
       <c r="AD119" s="16"/>
       <c r="AE119" s="16"/>
@@ -11786,7 +11817,7 @@
       <c r="E120" s="16"/>
       <c r="F120" s="16"/>
       <c r="G120" s="16"/>
-      <c r="H120" s="16"/>
+      <c r="H120" s="35"/>
       <c r="I120" s="16"/>
       <c r="J120" s="16"/>
       <c r="K120" s="16"/>
@@ -11805,8 +11836,8 @@
       <c r="X120" s="16"/>
       <c r="Y120" s="16"/>
       <c r="Z120" s="16"/>
-      <c r="AA120" s="16"/>
-      <c r="AB120" s="16"/>
+      <c r="AA120" s="35"/>
+      <c r="AB120" s="35"/>
       <c r="AC120" s="16"/>
       <c r="AD120" s="16"/>
       <c r="AE120" s="16"/>
@@ -11819,7 +11850,7 @@
       <c r="E121" s="16"/>
       <c r="F121" s="16"/>
       <c r="G121" s="16"/>
-      <c r="H121" s="16"/>
+      <c r="H121" s="35"/>
       <c r="I121" s="16"/>
       <c r="J121" s="16"/>
       <c r="K121" s="16"/>
@@ -11838,8 +11869,8 @@
       <c r="X121" s="16"/>
       <c r="Y121" s="16"/>
       <c r="Z121" s="16"/>
-      <c r="AA121" s="16"/>
-      <c r="AB121" s="16"/>
+      <c r="AA121" s="35"/>
+      <c r="AB121" s="35"/>
       <c r="AC121" s="16"/>
       <c r="AD121" s="16"/>
       <c r="AE121" s="16"/>
@@ -11852,7 +11883,7 @@
       <c r="E122" s="16"/>
       <c r="F122" s="16"/>
       <c r="G122" s="16"/>
-      <c r="H122" s="16"/>
+      <c r="H122" s="35"/>
       <c r="I122" s="16"/>
       <c r="J122" s="16"/>
       <c r="K122" s="16"/>
@@ -11871,8 +11902,8 @@
       <c r="X122" s="16"/>
       <c r="Y122" s="16"/>
       <c r="Z122" s="16"/>
-      <c r="AA122" s="16"/>
-      <c r="AB122" s="16"/>
+      <c r="AA122" s="35"/>
+      <c r="AB122" s="35"/>
       <c r="AC122" s="16"/>
       <c r="AD122" s="16"/>
       <c r="AE122" s="16"/>
@@ -11885,7 +11916,7 @@
       <c r="E123" s="16"/>
       <c r="F123" s="16"/>
       <c r="G123" s="16"/>
-      <c r="H123" s="16"/>
+      <c r="H123" s="35"/>
       <c r="I123" s="16"/>
       <c r="J123" s="16"/>
       <c r="K123" s="16"/>
@@ -11904,8 +11935,8 @@
       <c r="X123" s="16"/>
       <c r="Y123" s="16"/>
       <c r="Z123" s="16"/>
-      <c r="AA123" s="16"/>
-      <c r="AB123" s="16"/>
+      <c r="AA123" s="35"/>
+      <c r="AB123" s="35"/>
       <c r="AC123" s="16"/>
       <c r="AD123" s="16"/>
       <c r="AE123" s="16"/>
@@ -11918,7 +11949,7 @@
       <c r="E124" s="16"/>
       <c r="F124" s="16"/>
       <c r="G124" s="16"/>
-      <c r="H124" s="16"/>
+      <c r="H124" s="35"/>
       <c r="I124" s="16"/>
       <c r="J124" s="16"/>
       <c r="K124" s="16"/>
@@ -11937,8 +11968,8 @@
       <c r="X124" s="16"/>
       <c r="Y124" s="16"/>
       <c r="Z124" s="16"/>
-      <c r="AA124" s="16"/>
-      <c r="AB124" s="16"/>
+      <c r="AA124" s="35"/>
+      <c r="AB124" s="35"/>
       <c r="AC124" s="16"/>
       <c r="AD124" s="16"/>
       <c r="AE124" s="16"/>
@@ -11951,7 +11982,7 @@
       <c r="E125" s="16"/>
       <c r="F125" s="16"/>
       <c r="G125" s="16"/>
-      <c r="H125" s="16"/>
+      <c r="H125" s="35"/>
       <c r="I125" s="16"/>
       <c r="J125" s="16"/>
       <c r="K125" s="16"/>
@@ -11970,8 +12001,8 @@
       <c r="X125" s="16"/>
       <c r="Y125" s="16"/>
       <c r="Z125" s="16"/>
-      <c r="AA125" s="16"/>
-      <c r="AB125" s="16"/>
+      <c r="AA125" s="35"/>
+      <c r="AB125" s="35"/>
       <c r="AC125" s="16"/>
       <c r="AD125" s="16"/>
       <c r="AE125" s="16"/>
@@ -11984,7 +12015,7 @@
       <c r="E126" s="16"/>
       <c r="F126" s="16"/>
       <c r="G126" s="16"/>
-      <c r="H126" s="16"/>
+      <c r="H126" s="35"/>
       <c r="I126" s="16"/>
       <c r="J126" s="16"/>
       <c r="K126" s="16"/>
@@ -12003,8 +12034,8 @@
       <c r="X126" s="16"/>
       <c r="Y126" s="16"/>
       <c r="Z126" s="16"/>
-      <c r="AA126" s="16"/>
-      <c r="AB126" s="16"/>
+      <c r="AA126" s="35"/>
+      <c r="AB126" s="35"/>
       <c r="AC126" s="16"/>
       <c r="AD126" s="16"/>
       <c r="AE126" s="16"/>
@@ -12017,7 +12048,7 @@
       <c r="E127" s="16"/>
       <c r="F127" s="16"/>
       <c r="G127" s="16"/>
-      <c r="H127" s="16"/>
+      <c r="H127" s="35"/>
       <c r="I127" s="16"/>
       <c r="J127" s="16"/>
       <c r="K127" s="16"/>
@@ -12036,8 +12067,8 @@
       <c r="X127" s="16"/>
       <c r="Y127" s="16"/>
       <c r="Z127" s="16"/>
-      <c r="AA127" s="16"/>
-      <c r="AB127" s="16"/>
+      <c r="AA127" s="35"/>
+      <c r="AB127" s="35"/>
       <c r="AC127" s="16"/>
       <c r="AD127" s="16"/>
       <c r="AE127" s="16"/>
@@ -12050,7 +12081,7 @@
       <c r="E128" s="16"/>
       <c r="F128" s="16"/>
       <c r="G128" s="16"/>
-      <c r="H128" s="16"/>
+      <c r="H128" s="35"/>
       <c r="I128" s="16"/>
       <c r="J128" s="16"/>
       <c r="K128" s="16"/>
@@ -12069,8 +12100,8 @@
       <c r="X128" s="16"/>
       <c r="Y128" s="16"/>
       <c r="Z128" s="16"/>
-      <c r="AA128" s="16"/>
-      <c r="AB128" s="16"/>
+      <c r="AA128" s="35"/>
+      <c r="AB128" s="35"/>
       <c r="AC128" s="16"/>
       <c r="AD128" s="16"/>
       <c r="AE128" s="16"/>
@@ -12083,7 +12114,7 @@
       <c r="E129" s="16"/>
       <c r="F129" s="16"/>
       <c r="G129" s="16"/>
-      <c r="H129" s="16"/>
+      <c r="H129" s="35"/>
       <c r="I129" s="16"/>
       <c r="J129" s="16"/>
       <c r="K129" s="16"/>
@@ -12102,8 +12133,8 @@
       <c r="X129" s="16"/>
       <c r="Y129" s="16"/>
       <c r="Z129" s="16"/>
-      <c r="AA129" s="16"/>
-      <c r="AB129" s="16"/>
+      <c r="AA129" s="35"/>
+      <c r="AB129" s="35"/>
       <c r="AC129" s="16"/>
       <c r="AD129" s="16"/>
       <c r="AE129" s="16"/>
@@ -12116,7 +12147,7 @@
       <c r="E130" s="16"/>
       <c r="F130" s="16"/>
       <c r="G130" s="16"/>
-      <c r="H130" s="16"/>
+      <c r="H130" s="35"/>
       <c r="I130" s="16"/>
       <c r="J130" s="16"/>
       <c r="K130" s="16"/>
@@ -12135,8 +12166,8 @@
       <c r="X130" s="16"/>
       <c r="Y130" s="16"/>
       <c r="Z130" s="16"/>
-      <c r="AA130" s="16"/>
-      <c r="AB130" s="16"/>
+      <c r="AA130" s="35"/>
+      <c r="AB130" s="35"/>
       <c r="AC130" s="16"/>
       <c r="AD130" s="16"/>
       <c r="AE130" s="16"/>
@@ -12149,7 +12180,7 @@
       <c r="E131" s="16"/>
       <c r="F131" s="16"/>
       <c r="G131" s="16"/>
-      <c r="H131" s="16"/>
+      <c r="H131" s="35"/>
       <c r="I131" s="16"/>
       <c r="J131" s="16"/>
       <c r="K131" s="16"/>
@@ -12168,8 +12199,8 @@
       <c r="X131" s="16"/>
       <c r="Y131" s="16"/>
       <c r="Z131" s="16"/>
-      <c r="AA131" s="16"/>
-      <c r="AB131" s="16"/>
+      <c r="AA131" s="35"/>
+      <c r="AB131" s="35"/>
       <c r="AC131" s="16"/>
       <c r="AD131" s="16"/>
       <c r="AE131" s="16"/>
@@ -12182,7 +12213,7 @@
       <c r="E132" s="16"/>
       <c r="F132" s="16"/>
       <c r="G132" s="16"/>
-      <c r="H132" s="16"/>
+      <c r="H132" s="35"/>
       <c r="I132" s="16"/>
       <c r="J132" s="16"/>
       <c r="K132" s="16"/>
@@ -12201,8 +12232,8 @@
       <c r="X132" s="16"/>
       <c r="Y132" s="16"/>
       <c r="Z132" s="16"/>
-      <c r="AA132" s="16"/>
-      <c r="AB132" s="16"/>
+      <c r="AA132" s="35"/>
+      <c r="AB132" s="35"/>
       <c r="AC132" s="16"/>
       <c r="AD132" s="16"/>
       <c r="AE132" s="16"/>
@@ -12215,7 +12246,7 @@
       <c r="E133" s="16"/>
       <c r="F133" s="16"/>
       <c r="G133" s="16"/>
-      <c r="H133" s="16"/>
+      <c r="H133" s="35"/>
       <c r="I133" s="16"/>
       <c r="J133" s="16"/>
       <c r="K133" s="16"/>
@@ -12234,8 +12265,8 @@
       <c r="X133" s="16"/>
       <c r="Y133" s="16"/>
       <c r="Z133" s="16"/>
-      <c r="AA133" s="16"/>
-      <c r="AB133" s="16"/>
+      <c r="AA133" s="35"/>
+      <c r="AB133" s="35"/>
       <c r="AC133" s="16"/>
       <c r="AD133" s="16"/>
       <c r="AE133" s="16"/>
@@ -12248,7 +12279,7 @@
       <c r="E134" s="16"/>
       <c r="F134" s="16"/>
       <c r="G134" s="16"/>
-      <c r="H134" s="16"/>
+      <c r="H134" s="35"/>
       <c r="I134" s="16"/>
       <c r="J134" s="16"/>
       <c r="K134" s="16"/>
@@ -12267,8 +12298,8 @@
       <c r="X134" s="16"/>
       <c r="Y134" s="16"/>
       <c r="Z134" s="16"/>
-      <c r="AA134" s="16"/>
-      <c r="AB134" s="16"/>
+      <c r="AA134" s="35"/>
+      <c r="AB134" s="35"/>
       <c r="AC134" s="16"/>
       <c r="AD134" s="16"/>
       <c r="AE134" s="16"/>
@@ -12281,7 +12312,7 @@
       <c r="E135" s="16"/>
       <c r="F135" s="16"/>
       <c r="G135" s="16"/>
-      <c r="H135" s="16"/>
+      <c r="H135" s="35"/>
       <c r="I135" s="16"/>
       <c r="J135" s="16"/>
       <c r="K135" s="16"/>
@@ -12300,8 +12331,8 @@
       <c r="X135" s="16"/>
       <c r="Y135" s="16"/>
       <c r="Z135" s="16"/>
-      <c r="AA135" s="16"/>
-      <c r="AB135" s="16"/>
+      <c r="AA135" s="35"/>
+      <c r="AB135" s="35"/>
       <c r="AC135" s="16"/>
       <c r="AD135" s="16"/>
       <c r="AE135" s="16"/>
@@ -12314,7 +12345,7 @@
       <c r="E136" s="16"/>
       <c r="F136" s="16"/>
       <c r="G136" s="16"/>
-      <c r="H136" s="16"/>
+      <c r="H136" s="35"/>
       <c r="I136" s="16"/>
       <c r="J136" s="16"/>
       <c r="K136" s="16"/>
@@ -12333,8 +12364,8 @@
       <c r="X136" s="16"/>
       <c r="Y136" s="16"/>
       <c r="Z136" s="16"/>
-      <c r="AA136" s="16"/>
-      <c r="AB136" s="16"/>
+      <c r="AA136" s="35"/>
+      <c r="AB136" s="35"/>
       <c r="AC136" s="16"/>
       <c r="AD136" s="16"/>
       <c r="AE136" s="16"/>
@@ -12347,7 +12378,7 @@
       <c r="E137" s="16"/>
       <c r="F137" s="16"/>
       <c r="G137" s="16"/>
-      <c r="H137" s="16"/>
+      <c r="H137" s="35"/>
       <c r="I137" s="16"/>
       <c r="J137" s="16"/>
       <c r="K137" s="16"/>
@@ -12366,8 +12397,8 @@
       <c r="X137" s="16"/>
       <c r="Y137" s="16"/>
       <c r="Z137" s="16"/>
-      <c r="AA137" s="16"/>
-      <c r="AB137" s="16"/>
+      <c r="AA137" s="35"/>
+      <c r="AB137" s="35"/>
       <c r="AC137" s="16"/>
       <c r="AD137" s="16"/>
       <c r="AE137" s="16"/>
@@ -12380,7 +12411,7 @@
       <c r="E138" s="16"/>
       <c r="F138" s="16"/>
       <c r="G138" s="16"/>
-      <c r="H138" s="16"/>
+      <c r="H138" s="35"/>
       <c r="I138" s="16"/>
       <c r="J138" s="16"/>
       <c r="K138" s="16"/>
@@ -12399,8 +12430,8 @@
       <c r="X138" s="16"/>
       <c r="Y138" s="16"/>
       <c r="Z138" s="16"/>
-      <c r="AA138" s="16"/>
-      <c r="AB138" s="16"/>
+      <c r="AA138" s="35"/>
+      <c r="AB138" s="35"/>
       <c r="AC138" s="16"/>
       <c r="AD138" s="16"/>
       <c r="AE138" s="16"/>
@@ -12413,7 +12444,7 @@
       <c r="E139" s="16"/>
       <c r="F139" s="16"/>
       <c r="G139" s="16"/>
-      <c r="H139" s="16"/>
+      <c r="H139" s="35"/>
       <c r="I139" s="16"/>
       <c r="J139" s="16"/>
       <c r="K139" s="16"/>
@@ -12432,8 +12463,8 @@
       <c r="X139" s="16"/>
       <c r="Y139" s="16"/>
       <c r="Z139" s="16"/>
-      <c r="AA139" s="16"/>
-      <c r="AB139" s="16"/>
+      <c r="AA139" s="35"/>
+      <c r="AB139" s="35"/>
       <c r="AC139" s="16"/>
       <c r="AD139" s="16"/>
       <c r="AE139" s="16"/>
@@ -12446,7 +12477,7 @@
       <c r="E140" s="16"/>
       <c r="F140" s="16"/>
       <c r="G140" s="16"/>
-      <c r="H140" s="16"/>
+      <c r="H140" s="35"/>
       <c r="I140" s="16"/>
       <c r="J140" s="16"/>
       <c r="K140" s="16"/>
@@ -12465,8 +12496,8 @@
       <c r="X140" s="16"/>
       <c r="Y140" s="16"/>
       <c r="Z140" s="16"/>
-      <c r="AA140" s="16"/>
-      <c r="AB140" s="16"/>
+      <c r="AA140" s="35"/>
+      <c r="AB140" s="35"/>
       <c r="AC140" s="16"/>
       <c r="AD140" s="16"/>
       <c r="AE140" s="16"/>
